--- a/Design/Excel/ET/Datas/UnitConfig.xlsx
+++ b/Design/Excel/ET/Datas/UnitConfig.xlsx
@@ -1126,220 +1126,108 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
-  <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:9">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:9">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:9">
-      <c r="A3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5" spans="1:9">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1">
-        <v>1001</v>
-      </c>
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1">
-        <v>178</v>
-      </c>
-      <c r="I4" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:9">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1002</v>
-      </c>
-      <c r="C5" s="1">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
-      </c>
-      <c r="H5" s="1">
-        <v>278</v>
-      </c>
-      <c r="I5" s="1">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="28.5" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1003</v>
-      </c>
-      <c r="C6" s="1">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>178</v>
-      </c>
-      <c r="I6" s="1">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="28.5" spans="1:9">
-      <c r="A7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1004</v>
-      </c>
-      <c r="C7" s="1">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1">
-        <v>278</v>
-      </c>
-      <c r="I7" s="1">
-        <v>78</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr/>
+  <ns0:dimension ref="A1:I7"/>
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <ns0:cols>
+    <ns0:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <ns0:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <ns0:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <ns0:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <ns0:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <ns0:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <ns0:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <ns0:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <ns0:col min="11" max="16384" width="9" style="2"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" ht="16.5" spans="1:9">
+      <ns0:c r="A1" s="3" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="4" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="4" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="4"/>
+      <ns0:c r="E1" s="4" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="4" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="4" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="4" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" s="4" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" ht="16.5" spans="1:9">
+      <ns0:c r="A2" s="3" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="4" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="4" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="4"/>
+      <ns0:c r="E2" s="4" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="4" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="4" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="4" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" s="4" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" ht="16.5" spans="1:9">
+      <ns0:c r="A3" s="3" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="B3" s="4" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C3" s="4" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="4" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="4" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="4" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="4" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="4" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="I3" s="4" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ns0:pageSetup paperSize="9" orientation="portrait"/>
+  <ns0:headerFooter/>
+</ns0:worksheet>
 </file>